--- a/artfynd/A 62607-2021 artfynd.xlsx
+++ b/artfynd/A 62607-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62607-2021 artfynd.xlsx
+++ b/artfynd/A 62607-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7539,6 +7539,125 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>115007860</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>65</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Juoksuvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>832073</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7434337</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På  en stock till lämningarna efter timrad renhage.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62607-2021 artfynd.xlsx
+++ b/artfynd/A 62607-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3726,7 +3726,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101580390</v>
+        <v>101579436</v>
       </c>
       <c r="B28" t="n">
         <v>95525</v>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>832462.9409448111</v>
+        <v>832542.3015494493</v>
       </c>
       <c r="R28" t="n">
-        <v>7434234.301657814</v>
+        <v>7434349.304047841</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101579436</v>
+        <v>101577563</v>
       </c>
       <c r="B29" t="n">
         <v>95525</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>832542.3015494493</v>
+        <v>832423.5178254783</v>
       </c>
       <c r="R29" t="n">
-        <v>7434349.304047841</v>
+        <v>7434345.075220052</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3960,7 +3960,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101577563</v>
+        <v>101574303</v>
       </c>
       <c r="B30" t="n">
         <v>95525</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>832423.5178254783</v>
+        <v>832041.8369255165</v>
       </c>
       <c r="R30" t="n">
-        <v>7434345.075220052</v>
+        <v>7434233.978767255</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101574303</v>
+        <v>101576389</v>
       </c>
       <c r="B31" t="n">
         <v>95525</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>832041.8369255165</v>
+        <v>832227.4085375236</v>
       </c>
       <c r="R31" t="n">
-        <v>7434233.978767255</v>
+        <v>7434407.255121595</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101576389</v>
+        <v>101580575</v>
       </c>
       <c r="B32" t="n">
         <v>95525</v>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>832227.4085375236</v>
+        <v>832410.8716561554</v>
       </c>
       <c r="R32" t="n">
-        <v>7434407.255121595</v>
+        <v>7434243.81238648</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101580575</v>
+        <v>101577678</v>
       </c>
       <c r="B33" t="n">
         <v>95525</v>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>832410.8716561554</v>
+        <v>832407.6092308774</v>
       </c>
       <c r="R33" t="n">
-        <v>7434243.81238648</v>
+        <v>7434403.50834888</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4428,7 +4428,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101577678</v>
+        <v>101574540</v>
       </c>
       <c r="B34" t="n">
         <v>95525</v>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>832407.6092308774</v>
+        <v>832133.5165412206</v>
       </c>
       <c r="R34" t="n">
-        <v>7434403.50834888</v>
+        <v>7434336.171858103</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101574540</v>
+        <v>101577051</v>
       </c>
       <c r="B35" t="n">
         <v>95525</v>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>832133.5165412206</v>
+        <v>832085.306677701</v>
       </c>
       <c r="R35" t="n">
-        <v>7434336.171858103</v>
+        <v>7434213.477281552</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101577051</v>
+        <v>101576689</v>
       </c>
       <c r="B36" t="n">
         <v>95525</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>832085.306677701</v>
+        <v>832105.6784798002</v>
       </c>
       <c r="R36" t="n">
-        <v>7434213.477281552</v>
+        <v>7434251.724376834</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101576689</v>
+        <v>101580261</v>
       </c>
       <c r="B37" t="n">
         <v>95525</v>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>832105.6784798002</v>
+        <v>832561.9872950873</v>
       </c>
       <c r="R37" t="n">
-        <v>7434251.724376834</v>
+        <v>7434292.524526589</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101580261</v>
+        <v>101578059</v>
       </c>
       <c r="B38" t="n">
         <v>95525</v>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>832561.9872950873</v>
+        <v>832442.3716426172</v>
       </c>
       <c r="R38" t="n">
-        <v>7434292.524526589</v>
+        <v>7434346.988249134</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101578059</v>
+        <v>101580605</v>
       </c>
       <c r="B39" t="n">
         <v>95525</v>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>832442.3716426172</v>
+        <v>832381.6466296515</v>
       </c>
       <c r="R39" t="n">
-        <v>7434346.988249134</v>
+        <v>7434245.396313407</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101580605</v>
+        <v>101580072</v>
       </c>
       <c r="B40" t="n">
         <v>95525</v>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>832381.6466296515</v>
+        <v>832634.3079520713</v>
       </c>
       <c r="R40" t="n">
-        <v>7434245.396313407</v>
+        <v>7434354.624567165</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5247,7 +5247,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101580072</v>
+        <v>101577971</v>
       </c>
       <c r="B41" t="n">
         <v>95525</v>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>832634.3079520713</v>
+        <v>832492.465445805</v>
       </c>
       <c r="R41" t="n">
-        <v>7434354.624567165</v>
+        <v>7434408.742918122</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101577971</v>
+        <v>101579321</v>
       </c>
       <c r="B42" t="n">
         <v>95525</v>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>832492.465445805</v>
+        <v>832483.1804370482</v>
       </c>
       <c r="R42" t="n">
-        <v>7434408.742918122</v>
+        <v>7434299.550654875</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5481,57 +5481,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101579321</v>
+        <v>104154827</v>
       </c>
       <c r="B43" t="n">
-        <v>95525</v>
+        <v>77258</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>832483.1804370482</v>
+        <v>832195.1735810162</v>
       </c>
       <c r="R43" t="n">
-        <v>7434299.550654875</v>
+        <v>7434361.994383753</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5555,7 +5551,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5565,7 +5561,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5573,32 +5569,36 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104154827</v>
+        <v>104154825</v>
       </c>
       <c r="B44" t="n">
         <v>77258</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>832195.1735810162</v>
+        <v>832306.677536436</v>
       </c>
       <c r="R44" t="n">
-        <v>7434361.994383753</v>
+        <v>7434542.489819403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104154825</v>
+        <v>104154821</v>
       </c>
       <c r="B45" t="n">
-        <v>77258</v>
+        <v>78569</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5731,21 +5731,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>832306.677536436</v>
+        <v>832585.7639712588</v>
       </c>
       <c r="R45" t="n">
-        <v>7434542.489819403</v>
+        <v>7434461.890659626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104154821</v>
+        <v>104154803</v>
       </c>
       <c r="B46" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>832585.7639712588</v>
+        <v>832191.3132974848</v>
       </c>
       <c r="R46" t="n">
-        <v>7434461.890659626</v>
+        <v>7434438.983611122</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104154803</v>
+        <v>104154824</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
+        <v>77258</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5965,21 +5965,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5989,10 +5989,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>832191.3132974848</v>
+        <v>832379.6531289564</v>
       </c>
       <c r="R47" t="n">
-        <v>7434438.983611122</v>
+        <v>7434479.134234299</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104154824</v>
+        <v>104154822</v>
       </c>
       <c r="B48" t="n">
-        <v>77258</v>
+        <v>89356</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6078,25 +6078,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>832379.6531289564</v>
+        <v>832579.7751641127</v>
       </c>
       <c r="R48" t="n">
-        <v>7434479.134234299</v>
+        <v>7434475.060052222</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6183,7 +6183,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104154822</v>
+        <v>104154826</v>
       </c>
       <c r="B49" t="n">
         <v>89356</v>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>832579.7751641127</v>
+        <v>832243.5836381534</v>
       </c>
       <c r="R49" t="n">
-        <v>7434475.060052222</v>
+        <v>7434489.477652561</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104154826</v>
+        <v>104154823</v>
       </c>
       <c r="B50" t="n">
-        <v>89356</v>
+        <v>78569</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6312,25 +6312,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>832243.5836381534</v>
+        <v>832576.64099963</v>
       </c>
       <c r="R50" t="n">
-        <v>7434489.477652561</v>
+        <v>7434474.675812635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104154823</v>
+        <v>104187440</v>
       </c>
       <c r="B51" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6433,37 +6433,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>832576.64099963</v>
+        <v>832048.1157361974</v>
       </c>
       <c r="R51" t="n">
-        <v>7434474.675812635</v>
+        <v>7434202.171837158</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6497,17 +6497,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6522,22 +6517,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104187440</v>
+        <v>104187436</v>
       </c>
       <c r="B52" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6550,21 +6545,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6574,10 +6569,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>832048.1157361974</v>
+        <v>832284.7703927278</v>
       </c>
       <c r="R52" t="n">
-        <v>7434202.171837158</v>
+        <v>7434533.053441483</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6646,10 +6641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104187436</v>
+        <v>104187438</v>
       </c>
       <c r="B53" t="n">
-        <v>78569</v>
+        <v>89545</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6658,25 +6653,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6686,10 +6681,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>832284.7703927278</v>
+        <v>832182.1865014507</v>
       </c>
       <c r="R53" t="n">
-        <v>7434533.053441483</v>
+        <v>7434282.940133736</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6758,10 +6753,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104187438</v>
+        <v>104187441</v>
       </c>
       <c r="B54" t="n">
-        <v>89545</v>
+        <v>89633</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6774,21 +6769,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6798,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>832182.1865014507</v>
+        <v>832155.9361014101</v>
       </c>
       <c r="R54" t="n">
-        <v>7434282.940133736</v>
+        <v>7434224.506971988</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6870,10 +6865,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104187441</v>
+        <v>104187429</v>
       </c>
       <c r="B55" t="n">
-        <v>89633</v>
+        <v>89673</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6882,25 +6877,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6910,10 +6905,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>832155.9361014101</v>
+        <v>832223.4034415487</v>
       </c>
       <c r="R55" t="n">
-        <v>7434224.506971988</v>
+        <v>7434485.417244785</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6982,37 +6977,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104187429</v>
+        <v>104187433</v>
       </c>
       <c r="B56" t="n">
-        <v>89673</v>
+        <v>95525</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7022,10 +7017,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>832223.4034415487</v>
+        <v>832435.1202323985</v>
       </c>
       <c r="R56" t="n">
-        <v>7434485.417244785</v>
+        <v>7434363.976205058</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7094,7 +7089,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104187433</v>
+        <v>104187430</v>
       </c>
       <c r="B57" t="n">
         <v>95525</v>
@@ -7134,10 +7129,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>832435.1202323985</v>
+        <v>832315.0367837909</v>
       </c>
       <c r="R57" t="n">
-        <v>7434363.976205058</v>
+        <v>7434292.45636232</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7206,7 +7201,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104187430</v>
+        <v>104187431</v>
       </c>
       <c r="B58" t="n">
         <v>95525</v>
@@ -7246,10 +7241,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>832315.0367837909</v>
+        <v>832539.4390880878</v>
       </c>
       <c r="R58" t="n">
-        <v>7434292.45636232</v>
+        <v>7434340.213416044</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7318,53 +7313,57 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104187431</v>
+        <v>113888707</v>
       </c>
       <c r="B59" t="n">
-        <v>95525</v>
+        <v>91628</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>832539.4390880878</v>
+        <v>832076</v>
       </c>
       <c r="R59" t="n">
-        <v>7434340.213416044</v>
+        <v>7434230</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7388,22 +7387,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7418,22 +7412,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113888707</v>
+        <v>115007860</v>
       </c>
       <c r="B60" t="n">
-        <v>91628</v>
+        <v>90576</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7442,25 +7436,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7468,19 +7462,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>832076</v>
+        <v>832072</v>
       </c>
       <c r="R60" t="n">
-        <v>7434230</v>
+        <v>7434337</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7504,17 +7505,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>På  en stock till lämningarna efter timrad renhage.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7523,140 +7524,22 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>115007860</v>
-      </c>
-      <c r="B61" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>65</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Fläckporing</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Anthoporia albobrunnea</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Juoksuvaara, Nb</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>832072</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7434337</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Korpilombolo</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På  en stock till lämningarna efter timrad renhage.</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62607-2021 artfynd.xlsx
+++ b/artfynd/A 62607-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96602346</v>
+        <v>101577310</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Juoksuvaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>832356.020347836</v>
+        <v>832269</v>
       </c>
       <c r="R2" t="n">
-        <v>7434370.17468206</v>
+        <v>7434337</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,73 +764,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94025677</v>
+        <v>104187441</v>
       </c>
       <c r="B3" t="n">
-        <v>95526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224358</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Juoksuvaara, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>832455.800644154</v>
+        <v>832156</v>
       </c>
       <c r="R3" t="n">
-        <v>7434237.399421862</v>
+        <v>7434224</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,56 +855,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94025871</v>
+        <v>115007860</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,9 +906,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>832462.645064808</v>
+        <v>832072</v>
       </c>
       <c r="R4" t="n">
-        <v>7434233.470851087</v>
+        <v>7434337</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På  en stock till lämningarna efter timrad renhage.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,56 +987,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101574952</v>
+        <v>104187429</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>832244.5109683182</v>
+        <v>832223</v>
       </c>
       <c r="R5" t="n">
-        <v>7434488.399536925</v>
+        <v>7434485</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,22 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1154,63 +1077,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101578158</v>
+        <v>104187438</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>832376.9335003782</v>
+        <v>832182</v>
       </c>
       <c r="R6" t="n">
-        <v>7434316.326533983</v>
+        <v>7434283</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1163,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1270,44 +1174,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101575082</v>
+        <v>101579121</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>832279.1253922407</v>
+        <v>832409</v>
       </c>
       <c r="R7" t="n">
-        <v>7434527.198044535</v>
+        <v>7434298</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1353,19 +1252,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,56 +1282,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101575073</v>
+        <v>104154822</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>832279.1253922407</v>
+        <v>832579</v>
       </c>
       <c r="R8" t="n">
-        <v>7434527.198044535</v>
+        <v>7434475</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1347,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,34 +1366,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101574905</v>
+        <v>104154826</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,40 +1395,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>832211.5712498929</v>
+        <v>832243</v>
       </c>
       <c r="R9" t="n">
-        <v>7434491.118339339</v>
+        <v>7434490</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,22 +1449,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,34 +1468,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101577766</v>
+        <v>113888707</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,40 +1497,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>832446.0770720935</v>
+        <v>832076</v>
       </c>
       <c r="R10" t="n">
-        <v>7434456.288863902</v>
+        <v>7434230</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,22 +1555,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,56 +1574,50 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101575284</v>
+        <v>101618980</v>
       </c>
       <c r="B11" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,17 +1626,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>832362.8195422047</v>
+        <v>832088</v>
       </c>
       <c r="R11" t="n">
-        <v>7434558.106813533</v>
+        <v>7434250</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,19 +1663,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,56 +1693,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101575459</v>
+        <v>104154803</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>okänd, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>832367.2543344907</v>
+        <v>832191</v>
       </c>
       <c r="R12" t="n">
-        <v>7434512.174468274</v>
+        <v>7434439</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,22 +1758,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,76 +1777,66 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101580170</v>
+        <v>104187439</v>
       </c>
       <c r="B13" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>832582.600106596</v>
+        <v>832645</v>
       </c>
       <c r="R13" t="n">
-        <v>7434331.997268744</v>
+        <v>7434375</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2047,22 +1860,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,64 +1885,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101580243</v>
+        <v>104187440</v>
       </c>
       <c r="B14" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>832568.7356765086</v>
+        <v>832048</v>
       </c>
       <c r="R14" t="n">
-        <v>7434308.845257025</v>
+        <v>7434202</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2163,22 +1957,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,60 +1982,67 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101576287</v>
+        <v>96602346</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>832296.6937857189</v>
+        <v>832356</v>
       </c>
       <c r="R15" t="n">
-        <v>7434468.176517366</v>
+        <v>7434370</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2278,22 +2069,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,68 +2090,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101575411</v>
+        <v>104154824</v>
       </c>
       <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>832362.8195422047</v>
+        <v>832379</v>
       </c>
       <c r="R16" t="n">
-        <v>7434558.106813533</v>
+        <v>7434479</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2394,22 +2167,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,75 +2186,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101578342</v>
+        <v>104154825</v>
       </c>
       <c r="B17" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>832297.1248242147</v>
+        <v>832307</v>
       </c>
       <c r="R17" t="n">
-        <v>7434276.358235068</v>
+        <v>7434542</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2510,22 +2269,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2534,34 +2288,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101579280</v>
+        <v>104154827</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,41 +2317,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>832453.0364735168</v>
+        <v>832195</v>
       </c>
       <c r="R18" t="n">
-        <v>7434305.39095098</v>
+        <v>7434362</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2627,22 +2371,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,49 +2396,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101577310</v>
+        <v>101575062</v>
       </c>
       <c r="B19" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2712,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>832269.4255046446</v>
+        <v>832256</v>
       </c>
       <c r="R19" t="n">
-        <v>7434336.92406577</v>
+        <v>7434530</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2745,19 +2479,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,15 +2509,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101579121</v>
+        <v>101575073</v>
       </c>
       <c r="B20" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,21 +2520,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2828,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>832409.0513703715</v>
+        <v>832279</v>
       </c>
       <c r="R20" t="n">
-        <v>7434297.617709375</v>
+        <v>7434527</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2861,19 +2580,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2901,15 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101619542</v>
+        <v>101577766</v>
       </c>
       <c r="B21" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,21 +2621,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2940,17 +2644,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>832314.4746923407</v>
+        <v>832446</v>
       </c>
       <c r="R21" t="n">
-        <v>7434264.579134719</v>
+        <v>7434456</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2977,19 +2681,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,15 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101618980</v>
+        <v>101619411</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,21 +2722,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3060,13 +2749,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>832088.831018223</v>
+        <v>832284</v>
       </c>
       <c r="R22" t="n">
-        <v>7434249.662109124</v>
+        <v>7434536</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3093,19 +2782,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,15 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101619411</v>
+        <v>104154821</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,19 +2841,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>832284.7786515143</v>
+        <v>832585</v>
       </c>
       <c r="R23" t="n">
-        <v>7434536.232254928</v>
+        <v>7434462</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,22 +2877,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3230,76 +2896,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101577673</v>
+        <v>104154823</v>
       </c>
       <c r="B24" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Limingoån, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>832408.911269024</v>
+        <v>832576</v>
       </c>
       <c r="R24" t="n">
-        <v>7434376.654861754</v>
+        <v>7434475</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3323,27 +2979,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>En av många växtplatser i området</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3352,80 +2998,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101580629</v>
+        <v>104187436</v>
       </c>
       <c r="B25" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>832351.8778084635</v>
+        <v>832284</v>
       </c>
       <c r="R25" t="n">
-        <v>7434244.927575963</v>
+        <v>7434533</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3449,22 +3081,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,7 +3095,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3485,22 +3106,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101578093</v>
+        <v>101574865</v>
       </c>
       <c r="B26" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3508,27 +3124,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3536,10 +3151,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>832438.2619188194</v>
+        <v>832211</v>
       </c>
       <c r="R26" t="n">
-        <v>7434348.073675692</v>
+        <v>7434491</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3569,19 +3184,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3609,15 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101577284</v>
+        <v>101574952</v>
       </c>
       <c r="B27" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,27 +3225,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3653,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>832269.4255046446</v>
+        <v>832244</v>
       </c>
       <c r="R27" t="n">
-        <v>7434336.92406577</v>
+        <v>7434488</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3686,19 +3285,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3726,15 +3315,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101579436</v>
+        <v>101575082</v>
       </c>
       <c r="B28" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3742,27 +3326,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3770,10 +3353,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>832542.3015494493</v>
+        <v>832279</v>
       </c>
       <c r="R28" t="n">
-        <v>7434349.304047841</v>
+        <v>7434527</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3803,19 +3386,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3843,15 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101577563</v>
+        <v>101575411</v>
       </c>
       <c r="B29" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3859,27 +3427,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3887,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>832423.5178254783</v>
+        <v>832363</v>
       </c>
       <c r="R29" t="n">
-        <v>7434345.075220052</v>
+        <v>7434558</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3920,19 +3487,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3960,15 +3517,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101574303</v>
+        <v>101576287</v>
       </c>
       <c r="B30" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3976,27 +3528,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4004,10 +3555,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>832041.8369255165</v>
+        <v>832296</v>
       </c>
       <c r="R30" t="n">
-        <v>7434233.978767255</v>
+        <v>7434468</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4037,19 +3588,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4077,15 +3618,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101576389</v>
+        <v>101578158</v>
       </c>
       <c r="B31" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4093,27 +3629,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4121,10 +3656,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>832227.4085375236</v>
+        <v>832377</v>
       </c>
       <c r="R31" t="n">
-        <v>7434407.255121595</v>
+        <v>7434316</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4154,19 +3689,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4194,15 +3719,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101580575</v>
+        <v>101578342</v>
       </c>
       <c r="B32" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4210,27 +3730,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4238,10 +3757,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>832410.8716561554</v>
+        <v>832297</v>
       </c>
       <c r="R32" t="n">
-        <v>7434243.81238648</v>
+        <v>7434276</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4271,19 +3790,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4311,15 +3820,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101577678</v>
+        <v>101579620</v>
       </c>
       <c r="B33" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4327,27 +3831,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4355,10 +3858,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>832407.6092308774</v>
+        <v>832632</v>
       </c>
       <c r="R33" t="n">
-        <v>7434403.50834888</v>
+        <v>7434417</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4388,19 +3891,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4428,15 +3921,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101574540</v>
+        <v>101579648</v>
       </c>
       <c r="B34" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4444,27 +3932,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4472,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>832133.5165412206</v>
+        <v>832632</v>
       </c>
       <c r="R34" t="n">
-        <v>7434336.171858103</v>
+        <v>7434421</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4505,19 +3992,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4545,15 +4022,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101577051</v>
+        <v>101579643</v>
       </c>
       <c r="B35" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4561,27 +4033,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4589,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>832085.306677701</v>
+        <v>832621</v>
       </c>
       <c r="R35" t="n">
-        <v>7434213.477281552</v>
+        <v>7434424</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4622,19 +4093,9 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4662,15 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101576689</v>
+        <v>101579280</v>
       </c>
       <c r="B36" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4678,27 +4134,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4706,10 +4162,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>832105.6784798002</v>
+        <v>832453</v>
       </c>
       <c r="R36" t="n">
-        <v>7434251.724376834</v>
+        <v>7434305</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4739,28 +4195,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4779,15 +4224,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101580261</v>
+        <v>101580170</v>
       </c>
       <c r="B37" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4795,27 +4235,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4823,10 +4263,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>832561.9872950873</v>
+        <v>832582</v>
       </c>
       <c r="R37" t="n">
-        <v>7434292.524526589</v>
+        <v>7434332</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4856,28 +4296,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4896,15 +4325,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101578059</v>
+        <v>101580243</v>
       </c>
       <c r="B38" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4912,27 +4336,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4940,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>832442.3716426172</v>
+        <v>832569</v>
       </c>
       <c r="R38" t="n">
-        <v>7434346.988249134</v>
+        <v>7434308</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4973,28 +4397,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5013,15 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101580605</v>
+        <v>96602221</v>
       </c>
       <c r="B39" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5029,38 +4437,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>832381.6466296515</v>
+        <v>832570</v>
       </c>
       <c r="R39" t="n">
-        <v>7434245.396313407</v>
+        <v>7434413</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5087,22 +4503,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5111,34 +4517,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maj Aspebo, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101580072</v>
+        <v>101575127</v>
       </c>
       <c r="B40" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5146,27 +4546,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5174,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>832634.3079520713</v>
+        <v>832294</v>
       </c>
       <c r="R40" t="n">
-        <v>7434354.624567165</v>
+        <v>7434551</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5207,28 +4611,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5247,15 +4640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101577971</v>
+        <v>101576317</v>
       </c>
       <c r="B41" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5263,27 +4651,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5291,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>832492.465445805</v>
+        <v>832296</v>
       </c>
       <c r="R41" t="n">
-        <v>7434408.742918122</v>
+        <v>7434468</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5324,28 +4716,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5364,15 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101579321</v>
+        <v>101576431</v>
       </c>
       <c r="B42" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5380,27 +4756,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5408,10 +4788,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>832483.1804370482</v>
+        <v>832169</v>
       </c>
       <c r="R42" t="n">
-        <v>7434299.550654875</v>
+        <v>7434397</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5441,28 +4821,17 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5481,53 +4850,52 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104154827</v>
+        <v>101577661</v>
       </c>
       <c r="B43" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>832195.1735810162</v>
+        <v>832409</v>
       </c>
       <c r="R43" t="n">
-        <v>7434361.994383753</v>
+        <v>7434377</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5551,27 +4919,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5586,65 +4939,64 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104154825</v>
+        <v>101577685</v>
       </c>
       <c r="B44" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>832306.677536436</v>
+        <v>832408</v>
       </c>
       <c r="R44" t="n">
-        <v>7434542.489819403</v>
+        <v>7434404</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5668,27 +5020,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,65 +5040,64 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104154821</v>
+        <v>101580524</v>
       </c>
       <c r="B45" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>832585.7639712588</v>
+        <v>832417</v>
       </c>
       <c r="R45" t="n">
-        <v>7434461.890659626</v>
+        <v>7434252</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5785,27 +5121,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5820,65 +5141,68 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104154803</v>
+        <v>101580560</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>832191.3132974848</v>
+        <v>832410</v>
       </c>
       <c r="R46" t="n">
-        <v>7434438.983611122</v>
+        <v>7434244</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5902,27 +5226,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5937,27 +5246,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104154824</v>
+        <v>104187437</v>
       </c>
       <c r="B47" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5965,37 +5269,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Juoksovaara, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>832379.6531289564</v>
+        <v>832543</v>
       </c>
       <c r="R47" t="n">
-        <v>7434479.134234299</v>
+        <v>7434413</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6019,27 +5323,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,27 +5343,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104154822</v>
+        <v>94025871</v>
       </c>
       <c r="B48" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,37 +5366,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>832579.7751641127</v>
+        <v>832463</v>
       </c>
       <c r="R48" t="n">
-        <v>7434475.060052222</v>
+        <v>7434234</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6136,27 +5428,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6165,33 +5442,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104154826</v>
+        <v>94025907</v>
       </c>
       <c r="B49" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6199,37 +5472,49 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Juoksuvaara, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>832243.5836381534</v>
+        <v>832482</v>
       </c>
       <c r="R49" t="n">
-        <v>7434489.477652561</v>
+        <v>7434233</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6253,27 +5538,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6282,71 +5552,71 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104154823</v>
+        <v>101574297</v>
       </c>
       <c r="B50" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>832576.64099963</v>
+        <v>832042</v>
       </c>
       <c r="R50" t="n">
-        <v>7434474.675812635</v>
+        <v>7434234</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6370,27 +5640,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6399,71 +5654,71 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104187440</v>
+        <v>101574540</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>832048.1157361974</v>
+        <v>832133</v>
       </c>
       <c r="R51" t="n">
-        <v>7434202.171837158</v>
+        <v>7434337</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6487,22 +5742,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6511,6 +5756,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6522,60 +5768,59 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104187436</v>
+        <v>101575146</v>
       </c>
       <c r="B52" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>832284.7703927278</v>
+        <v>832316</v>
       </c>
       <c r="R52" t="n">
-        <v>7434533.053441483</v>
+        <v>7434579</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6599,22 +5844,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6623,6 +5858,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6634,60 +5870,59 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104187438</v>
+        <v>101576389</v>
       </c>
       <c r="B53" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>832182.1865014507</v>
+        <v>832228</v>
       </c>
       <c r="R53" t="n">
-        <v>7434282.940133736</v>
+        <v>7434407</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6711,22 +5946,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6735,6 +5960,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6746,60 +5972,59 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104187441</v>
+        <v>101576689</v>
       </c>
       <c r="B54" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>832155.9361014101</v>
+        <v>832106</v>
       </c>
       <c r="R54" t="n">
-        <v>7434224.506971988</v>
+        <v>7434251</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6823,22 +6048,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6847,6 +6062,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6858,60 +6074,59 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104187429</v>
+        <v>101577051</v>
       </c>
       <c r="B55" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>832223.4034415487</v>
+        <v>832085</v>
       </c>
       <c r="R55" t="n">
-        <v>7434485.417244785</v>
+        <v>7434214</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6935,22 +6150,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6959,6 +6164,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6970,22 +6176,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104187433</v>
+        <v>101577284</v>
       </c>
       <c r="B56" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7011,19 +6212,23 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>832435.1202323985</v>
+        <v>832269</v>
       </c>
       <c r="R56" t="n">
-        <v>7434363.976205058</v>
+        <v>7434337</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7047,22 +6252,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7071,6 +6266,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7082,22 +6278,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104187430</v>
+        <v>101577563</v>
       </c>
       <c r="B57" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7123,19 +6314,23 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>832315.0367837909</v>
+        <v>832423</v>
       </c>
       <c r="R57" t="n">
-        <v>7434292.45636232</v>
+        <v>7434345</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7159,22 +6354,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7183,6 +6368,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7194,22 +6380,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104187431</v>
+        <v>101577673</v>
       </c>
       <c r="B58" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7235,19 +6416,23 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Juoksovaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>832539.4390880878</v>
+        <v>832409</v>
       </c>
       <c r="R58" t="n">
-        <v>7434340.213416044</v>
+        <v>7434377</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7271,22 +6456,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>En av många växtplatser i området</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7295,6 +6475,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7306,64 +6487,59 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113888707</v>
+        <v>101577678</v>
       </c>
       <c r="B59" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Limingoån, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>832076</v>
+        <v>832408</v>
       </c>
       <c r="R59" t="n">
-        <v>7434230</v>
+        <v>7434404</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7387,17 +6563,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7406,82 +6577,71 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Maj Aspebo, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115007860</v>
+        <v>101577971</v>
       </c>
       <c r="B60" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Juoksuvaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>832072</v>
+        <v>832493</v>
       </c>
       <c r="R60" t="n">
-        <v>7434337</v>
+        <v>7434408</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7505,17 +6665,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På  en stock till lämningarna efter timrad renhage.</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7531,15 +6686,2048 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>101578059</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>832442</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7434347</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>101578093</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>832438</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7434348</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>101579321</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>832483</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7434299</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>101579436</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>832542</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7434349</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>101580072</v>
+      </c>
+      <c r="B65" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>832634</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7434355</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>101580261</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>832562</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7434293</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>101580353</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>832475</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7434232</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>101580575</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>832410</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7434244</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>101580605</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>832381</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7434245</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>101580629</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>832351</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7434245</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>104187430</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Juoksovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>832315</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7434292</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>104187431</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Juoksovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>832539</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7434340</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>104187433</v>
+      </c>
+      <c r="B73" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Juoksovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>832435</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7434364</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>104187434</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Juoksovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>832005</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7434192</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2022-10-17</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>101619705</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Juoksovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>832627</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7434454</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>94025600</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97990</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Juoksuvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>832451</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7434224</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>94025677</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97990</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Juoksuvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>832456</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7434237</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>101575284</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>832363</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7434558</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>101575459</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>okänd, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>832368</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7434513</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>101619542</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Juoksovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>832314</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7434265</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62607-2021 artfynd.xlsx
+++ b/artfynd/A 62607-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115007860</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187429</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187438</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579121</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154826</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888707</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101618980</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1690,6 +1740,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154803</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187440</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96602346</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154824</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154825</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2206,6 +2281,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154827</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575062</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2408,6 +2493,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575073</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2509,6 +2599,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101619411</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2606,6 +2701,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187436</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2707,6 +2807,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101574865</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2808,6 +2913,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101574952</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2909,6 +3019,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575082</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3010,6 +3125,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575411</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3111,6 +3231,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101576287</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3212,6 +3337,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101578158</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3313,6 +3443,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101578342</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3418,6 +3553,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575127</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3523,6 +3663,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101576317</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3628,6 +3773,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101576431</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3729,6 +3879,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577661</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3830,6 +3985,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577685</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3931,6 +4091,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580524</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4036,6 +4201,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580560</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4138,6 +4308,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101574297</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4240,6 +4415,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101574540</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4342,6 +4522,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575146</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4444,6 +4629,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101576389</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4546,6 +4736,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101576689</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4648,6 +4843,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577051</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4750,6 +4950,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577284</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4852,6 +5057,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577563</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4959,6 +5169,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577673</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5061,6 +5276,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577678</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5163,6 +5383,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580575</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5265,6 +5490,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580605</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5371,6 +5601,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580629</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5468,6 +5703,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187430</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5565,6 +5805,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187434</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5666,6 +5911,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575284</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5767,6 +6017,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101575459</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5868,6 +6123,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101619542</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5970,6 +6230,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154822</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6067,6 +6332,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187439</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6168,6 +6438,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577766</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6270,6 +6545,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154821</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6372,6 +6652,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104154823</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6473,6 +6758,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579620</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6574,6 +6864,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579648</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6675,6 +6970,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579643</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6776,6 +7076,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579280</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6877,6 +7182,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580170</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6978,6 +7288,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580243</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7087,6 +7402,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96602221</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7184,6 +7504,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187437</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7290,6 +7615,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94025871</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7400,6 +7730,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94025907</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7502,6 +7837,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101577971</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7604,6 +7944,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101578059</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7706,6 +8051,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101578093</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7808,6 +8158,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579321</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7910,6 +8265,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101579436</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8012,6 +8372,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580072</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8114,6 +8479,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580261</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8216,6 +8586,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101580353</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8313,6 +8688,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187431</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8410,6 +8790,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104187433</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8516,6 +8901,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101619705</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8622,6 +9012,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94025600</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8728,8 +9123,94 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94025677</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>